--- a/examples/STG_Surface/stations.xlsx
+++ b/examples/STG_Surface/stations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\01. Brain\11. GitHub\ShakerMakerResults\examples\STG_Surface\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78BDF7C-A64D-4607-A38A-8CCA0DB3F750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC21B730-08F8-4905-BB25-9E7DF172C497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stations" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Station</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>utm_0</t>
+  </si>
+  <si>
+    <t>CEN</t>
   </si>
 </sst>
 </file>
@@ -404,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
@@ -579,7 +582,22 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>358265.57163999998</v>
+      </c>
+      <c r="C13">
+        <v>6300158.0241999999</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>